--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential India Opportunities Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential India Opportunities Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="215">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential India Opportunities Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -52,7 +52,7 @@
     <t>Yield to Call @</t>
   </si>
   <si>
-    <t>Equity &amp; Equity Related Instruments (Note -1)</t>
+    <t>Equity &amp; Equity Related Instruments</t>
   </si>
   <si>
     <t/>
@@ -61,19 +61,37 @@
     <t>Listed / Awaiting Listing On Stock Exchanges</t>
   </si>
   <si>
+    <t>Axis Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE238A01034</t>
+  </si>
+  <si>
+    <t>Banks</t>
+  </si>
+  <si>
     <t>HDFC Bank Ltd.</t>
   </si>
   <si>
     <t>INE040A01034</t>
   </si>
   <si>
-    <t>Banks</t>
-  </si>
-  <si>
-    <t>Axis Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE238A01034</t>
+    <t>Reliance Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE002A01018</t>
+  </si>
+  <si>
+    <t>Petroleum Products</t>
+  </si>
+  <si>
+    <t>Sun Pharmaceutical Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE044A01036</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals &amp; Biotechnology</t>
   </si>
   <si>
     <t>ICICI Bank Ltd.</t>
@@ -82,6 +100,15 @@
     <t>INE090A01021</t>
   </si>
   <si>
+    <t>Bharti Airtel Ltd.</t>
+  </si>
+  <si>
+    <t>INE397D01024</t>
+  </si>
+  <si>
+    <t>Telecom - Services</t>
+  </si>
+  <si>
     <t>Infosys Ltd.</t>
   </si>
   <si>
@@ -91,22 +118,49 @@
     <t>It - Software</t>
   </si>
   <si>
-    <t>Bharti Airtel Ltd.</t>
-  </si>
-  <si>
-    <t>INE397D01024</t>
-  </si>
-  <si>
-    <t>Telecom - Services</t>
-  </si>
-  <si>
-    <t>Sun Pharmaceutical Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE044A01036</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals &amp; Biotechnology</t>
+    <t>State Bank Of India</t>
+  </si>
+  <si>
+    <t>INE062A01020</t>
+  </si>
+  <si>
+    <t>SBI Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE123W01016</t>
+  </si>
+  <si>
+    <t>Insurance</t>
+  </si>
+  <si>
+    <t>Maruti Suzuki India Ltd.</t>
+  </si>
+  <si>
+    <t>INE585B01010</t>
+  </si>
+  <si>
+    <t>Automobiles</t>
+  </si>
+  <si>
+    <t>HDFC Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE795G01014</t>
+  </si>
+  <si>
+    <t>ICICI Lombard General Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE765G01017</t>
+  </si>
+  <si>
+    <t>Oil &amp; Natural Gas Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE213A01029</t>
+  </si>
+  <si>
+    <t>Oil</t>
   </si>
   <si>
     <t>IndusInd Bank Ltd.</t>
@@ -115,13 +169,28 @@
     <t>INE095A01012</t>
   </si>
   <si>
-    <t>Maruti Suzuki India Ltd.</t>
-  </si>
-  <si>
-    <t>INE585B01010</t>
-  </si>
-  <si>
-    <t>Automobiles</t>
+    <t>Larsen &amp; Toubro Ltd.</t>
+  </si>
+  <si>
+    <t>INE018A01030</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
+    <t>NTPC Ltd.</t>
+  </si>
+  <si>
+    <t>INE733E01010</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>Tata Motors Ltd.</t>
+  </si>
+  <si>
+    <t>INE155A01022</t>
   </si>
   <si>
     <t>Hindustan Unilever Ltd.</t>
@@ -133,67 +202,31 @@
     <t>Diversified Fmcg</t>
   </si>
   <si>
-    <t>HDFC Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE795G01014</t>
-  </si>
-  <si>
-    <t>Insurance</t>
-  </si>
-  <si>
-    <t>State Bank Of India</t>
-  </si>
-  <si>
-    <t>INE062A01020</t>
-  </si>
-  <si>
-    <t>ICICI Lombard General Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE765G01017</t>
-  </si>
-  <si>
-    <t>SBI Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE123W01016</t>
-  </si>
-  <si>
-    <t>Oil &amp; Natural Gas Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE213A01029</t>
-  </si>
-  <si>
-    <t>Oil</t>
-  </si>
-  <si>
-    <t>NTPC Ltd.</t>
-  </si>
-  <si>
-    <t>INE733E01010</t>
-  </si>
-  <si>
-    <t>Power</t>
-  </si>
-  <si>
-    <t>Larsen &amp; Toubro Ltd.</t>
-  </si>
-  <si>
-    <t>INE018A01030</t>
-  </si>
-  <si>
-    <t>Construction</t>
-  </si>
-  <si>
-    <t>Reliance Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE002A01018</t>
-  </si>
-  <si>
-    <t>Petroleum Products</t>
+    <t>PI Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE603J01030</t>
+  </si>
+  <si>
+    <t>Fertilizers &amp; Agrochemicals</t>
+  </si>
+  <si>
+    <t>Vedanta Ltd.</t>
+  </si>
+  <si>
+    <t>INE205A01025</t>
+  </si>
+  <si>
+    <t>Diversified Metals</t>
+  </si>
+  <si>
+    <t>Interglobe Aviation Ltd.</t>
+  </si>
+  <si>
+    <t>INE646L01027</t>
+  </si>
+  <si>
+    <t>Transport Services</t>
   </si>
   <si>
     <t>Avenue Supermarts Ltd.</t>
@@ -217,97 +250,298 @@
     <t>INE406A01037</t>
   </si>
   <si>
+    <t>Dr. Reddy's Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE089A01031</t>
+  </si>
+  <si>
+    <t>Mahindra &amp; Mahindra Ltd.</t>
+  </si>
+  <si>
+    <t>INE101A01026</t>
+  </si>
+  <si>
     <t>Alkem Laboratories Ltd.</t>
   </si>
   <si>
     <t>INE540L01014</t>
   </si>
   <si>
-    <t>Shree Cements Ltd.</t>
-  </si>
-  <si>
-    <t>INE070A01015</t>
+    <t>Indian Energy Exchange Ltd.</t>
+  </si>
+  <si>
+    <t>INE022Q01020</t>
+  </si>
+  <si>
+    <t>Capital Markets</t>
+  </si>
+  <si>
+    <t>Star Health &amp; Allied Insurance</t>
+  </si>
+  <si>
+    <t>INE575P01011</t>
+  </si>
+  <si>
+    <t>ITC Ltd.</t>
+  </si>
+  <si>
+    <t>INE154A01025</t>
+  </si>
+  <si>
+    <t>Info Edge (India) Ltd.</t>
+  </si>
+  <si>
+    <t>INE663F01032</t>
+  </si>
+  <si>
+    <t>Affle India Ltd.</t>
+  </si>
+  <si>
+    <t>INE00WC01027</t>
+  </si>
+  <si>
+    <t>It - Services</t>
+  </si>
+  <si>
+    <t>Tata Chemicals Ltd.</t>
+  </si>
+  <si>
+    <t>INE092A01019</t>
+  </si>
+  <si>
+    <t>Chemicals &amp; Petrochemicals</t>
+  </si>
+  <si>
+    <t>ICICI Prudential Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE726G01019</t>
+  </si>
+  <si>
+    <t>Balkrishna Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE787D01026</t>
+  </si>
+  <si>
+    <t>Auto Components</t>
+  </si>
+  <si>
+    <t>Kalpataru Projects International Ltd</t>
+  </si>
+  <si>
+    <t>INE220B01022</t>
+  </si>
+  <si>
+    <t>Jindal Steel &amp; Power Ltd.</t>
+  </si>
+  <si>
+    <t>INE749A01030</t>
+  </si>
+  <si>
+    <t>Ferrous Metals</t>
+  </si>
+  <si>
+    <t>UPL Ltd.</t>
+  </si>
+  <si>
+    <t>INE628A01036</t>
+  </si>
+  <si>
+    <t>Zydus Lifesciences Ltd.</t>
+  </si>
+  <si>
+    <t>INE010B01027</t>
+  </si>
+  <si>
+    <t>Gujarat State Petronet Ltd.</t>
+  </si>
+  <si>
+    <t>INE246F01010</t>
+  </si>
+  <si>
+    <t>Gas</t>
+  </si>
+  <si>
+    <t>Tata Communications Ltd.</t>
+  </si>
+  <si>
+    <t>INE151A01013</t>
+  </si>
+  <si>
+    <t>Bharat Forge Ltd.</t>
+  </si>
+  <si>
+    <t>INE465A01025</t>
+  </si>
+  <si>
+    <t>Tata Steel Ltd.</t>
+  </si>
+  <si>
+    <t>INE081A01020</t>
+  </si>
+  <si>
+    <t>Oil India Ltd.</t>
+  </si>
+  <si>
+    <t>INE274J01014</t>
+  </si>
+  <si>
+    <t>Aarti Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE769A01020</t>
+  </si>
+  <si>
+    <t>TBO Tek Ltd.</t>
+  </si>
+  <si>
+    <t>INE673O01025</t>
+  </si>
+  <si>
+    <t>Leisure Services</t>
+  </si>
+  <si>
+    <t>CIE Automotive India Ltd</t>
+  </si>
+  <si>
+    <t>INE536H01010</t>
+  </si>
+  <si>
+    <t>Syngene International Ltd.</t>
+  </si>
+  <si>
+    <t>INE398R01022</t>
+  </si>
+  <si>
+    <t>Healthcare Services</t>
+  </si>
+  <si>
+    <t>The Great Eastern Shipping Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE017A01032</t>
+  </si>
+  <si>
+    <t>Cyient Ltd.</t>
+  </si>
+  <si>
+    <t>INE136B01020</t>
+  </si>
+  <si>
+    <t>Chemplast Sanmar Ltd</t>
+  </si>
+  <si>
+    <t>INE488A01050</t>
+  </si>
+  <si>
+    <t>PNC Infratech Ltd.</t>
+  </si>
+  <si>
+    <t>INE195J01029</t>
+  </si>
+  <si>
+    <t>Bharat Petroleum Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE029A01011</t>
+  </si>
+  <si>
+    <t>Zomato Ltd.</t>
+  </si>
+  <si>
+    <t>INE758T01015</t>
+  </si>
+  <si>
+    <t>Medplus Health Services Ltd</t>
+  </si>
+  <si>
+    <t>INE804L01022</t>
+  </si>
+  <si>
+    <t>Cartrade Tech Ltd</t>
+  </si>
+  <si>
+    <t>INE290S01011</t>
+  </si>
+  <si>
+    <t>Britannia Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE216A01030</t>
+  </si>
+  <si>
+    <t>Food Products</t>
+  </si>
+  <si>
+    <t>Bata India Ltd.</t>
+  </si>
+  <si>
+    <t>INE176A01028</t>
+  </si>
+  <si>
+    <t>Consumer Durables</t>
+  </si>
+  <si>
+    <t>Apollo Tyres Ltd.</t>
+  </si>
+  <si>
+    <t>INE438A01022</t>
+  </si>
+  <si>
+    <t>Rural Electrification Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE020B01018</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Thyrocare Technologies Ltd.</t>
+  </si>
+  <si>
+    <t>INE594H01019</t>
+  </si>
+  <si>
+    <t>PVR INOX Ltd.</t>
+  </si>
+  <si>
+    <t>INE191H01014</t>
+  </si>
+  <si>
+    <t>Entertainment</t>
+  </si>
+  <si>
+    <t>UPL Ltd. (Right Share)</t>
+  </si>
+  <si>
+    <t>IN9628A01026</t>
+  </si>
+  <si>
+    <t>AIA Engineering Ltd.</t>
+  </si>
+  <si>
+    <t>INE212H01026</t>
+  </si>
+  <si>
+    <t>Industrial Products</t>
+  </si>
+  <si>
+    <t>The India Cements Ltd.</t>
+  </si>
+  <si>
+    <t>INE383A01012</t>
   </si>
   <si>
     <t>Cement &amp; Cement Products</t>
   </si>
   <si>
-    <t>UPL Ltd.</t>
-  </si>
-  <si>
-    <t>INE628A01036</t>
-  </si>
-  <si>
-    <t>Fertilizers &amp; Agrochemicals</t>
-  </si>
-  <si>
-    <t>Info Edge (India) Ltd.</t>
-  </si>
-  <si>
-    <t>INE663F01024</t>
-  </si>
-  <si>
-    <t>The Ramco Cements Ltd.</t>
-  </si>
-  <si>
-    <t>INE331A01037</t>
-  </si>
-  <si>
-    <t>ITC Ltd.</t>
-  </si>
-  <si>
-    <t>INE154A01025</t>
-  </si>
-  <si>
-    <t>Cartrade Tech Ltd</t>
-  </si>
-  <si>
-    <t>INE290S01011</t>
-  </si>
-  <si>
-    <t>PI Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE603J01030</t>
-  </si>
-  <si>
-    <t>Indian Energy Exchange Ltd.</t>
-  </si>
-  <si>
-    <t>INE022Q01020</t>
-  </si>
-  <si>
-    <t>Capital Markets</t>
-  </si>
-  <si>
-    <t>Affle India Ltd.</t>
-  </si>
-  <si>
-    <t>INE00WC01027</t>
-  </si>
-  <si>
-    <t>It - Services</t>
-  </si>
-  <si>
-    <t>Tata Motors Ltd.</t>
-  </si>
-  <si>
-    <t>INE155A01022</t>
-  </si>
-  <si>
-    <t>Tata Steel Ltd.</t>
-  </si>
-  <si>
-    <t>INE081A01020</t>
-  </si>
-  <si>
-    <t>Ferrous Metals</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE726G01019</t>
+    <t>IRB Infrastructure Developers Ltd.</t>
+  </si>
+  <si>
+    <t>INE821I01022</t>
   </si>
   <si>
     <t>FSN E-Commerce Ventures Ltd.</t>
@@ -316,205 +550,10 @@
     <t>INE388Y01029</t>
   </si>
   <si>
-    <t>Tata Chemicals Ltd.</t>
-  </si>
-  <si>
-    <t>INE092A01019</t>
-  </si>
-  <si>
-    <t>Chemicals &amp; Petrochemicals</t>
-  </si>
-  <si>
-    <t>Kalpataru Projects International Ltd</t>
-  </si>
-  <si>
-    <t>INE220B01022</t>
-  </si>
-  <si>
-    <t>Jindal Steel &amp; Power Ltd.</t>
-  </si>
-  <si>
-    <t>INE749A01030</t>
-  </si>
-  <si>
-    <t>TVS Motor Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE494B01023</t>
-  </si>
-  <si>
-    <t>Gujarat State Petronet Ltd.</t>
-  </si>
-  <si>
-    <t>INE246F01010</t>
-  </si>
-  <si>
-    <t>Gas</t>
-  </si>
-  <si>
-    <t>Star Health &amp; Allied Insurance</t>
-  </si>
-  <si>
-    <t>INE575P01011</t>
-  </si>
-  <si>
-    <t>Dalmia Bharat Ltd.</t>
-  </si>
-  <si>
-    <t>INE00R701025</t>
-  </si>
-  <si>
-    <t>SBI Cards &amp; Payment Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE018E01016</t>
-  </si>
-  <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>Bharat Forge Ltd.</t>
-  </si>
-  <si>
-    <t>INE465A01025</t>
-  </si>
-  <si>
-    <t>Auto Components</t>
-  </si>
-  <si>
-    <t>Balkrishna Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE787D01026</t>
-  </si>
-  <si>
-    <t>Zydus Lifesciences Ltd.</t>
-  </si>
-  <si>
-    <t>INE010B01027</t>
-  </si>
-  <si>
-    <t>Aarti Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE769A01020</t>
-  </si>
-  <si>
-    <t>CIE Automotive India Ltd</t>
-  </si>
-  <si>
-    <t>INE536H01010</t>
-  </si>
-  <si>
-    <t>The Great Eastern Shipping Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE017A01032</t>
-  </si>
-  <si>
-    <t>Transport Services</t>
-  </si>
-  <si>
-    <t>Bata India Ltd.</t>
-  </si>
-  <si>
-    <t>INE176A01028</t>
-  </si>
-  <si>
-    <t>Consumer Durables</t>
-  </si>
-  <si>
-    <t>Cyient Ltd.</t>
-  </si>
-  <si>
-    <t>INE136B01020</t>
-  </si>
-  <si>
-    <t>PNC Infratech Ltd.</t>
-  </si>
-  <si>
-    <t>INE195J01029</t>
-  </si>
-  <si>
-    <t>Chemplast Sanmar Ltd</t>
-  </si>
-  <si>
-    <t>INE488A01050</t>
-  </si>
-  <si>
-    <t>Interglobe Aviation Ltd.</t>
-  </si>
-  <si>
-    <t>INE646L01027</t>
-  </si>
-  <si>
-    <t>Oil India Ltd.</t>
-  </si>
-  <si>
-    <t>INE274J01014</t>
-  </si>
-  <si>
-    <t>Ambuja Cements Ltd.</t>
-  </si>
-  <si>
-    <t>INE079A01024</t>
-  </si>
-  <si>
-    <t>Medplus Health Services Ltd</t>
-  </si>
-  <si>
-    <t>INE804L01022</t>
-  </si>
-  <si>
-    <t>Zomato Ltd.</t>
-  </si>
-  <si>
-    <t>INE758T01015</t>
-  </si>
-  <si>
-    <t>Syngene International Ltd.</t>
-  </si>
-  <si>
-    <t>INE398R01022</t>
-  </si>
-  <si>
-    <t>Healthcare Services</t>
-  </si>
-  <si>
-    <t>Thyrocare Technologies Ltd.</t>
-  </si>
-  <si>
-    <t>INE594H01019</t>
-  </si>
-  <si>
-    <t>PVR INOX Ltd.</t>
-  </si>
-  <si>
-    <t>INE191H01014</t>
-  </si>
-  <si>
-    <t>Entertainment</t>
-  </si>
-  <si>
-    <t>Cipla Ltd.</t>
-  </si>
-  <si>
-    <t>INE059A01026</t>
-  </si>
-  <si>
-    <t>UPL Ltd. (Right Share)</t>
-  </si>
-  <si>
-    <t>IN9628A01018</t>
-  </si>
-  <si>
-    <t>AIA Engineering Ltd.</t>
-  </si>
-  <si>
-    <t>INE212H01026</t>
-  </si>
-  <si>
-    <t>Industrial Products</t>
+    <t>Gujarat Gas Ltd.</t>
+  </si>
+  <si>
+    <t>INE844O01030</t>
   </si>
   <si>
     <t>Bajaj Electricals Ltd.</t>
@@ -523,42 +562,6 @@
     <t>INE193E01025</t>
   </si>
   <si>
-    <t>The India Cements Ltd.</t>
-  </si>
-  <si>
-    <t>INE383A01012</t>
-  </si>
-  <si>
-    <t>ITC Hotels Ltd</t>
-  </si>
-  <si>
-    <t>INE379A01028</t>
-  </si>
-  <si>
-    <t>Leisure Services</t>
-  </si>
-  <si>
-    <t>Gujarat Gas Ltd.</t>
-  </si>
-  <si>
-    <t>INE844O01030</t>
-  </si>
-  <si>
-    <t>Kotak Mahindra Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE237A01028</t>
-  </si>
-  <si>
-    <t>Birla Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE340A01012</t>
-  </si>
-  <si>
-    <t>^</t>
-  </si>
-  <si>
     <t>Unlisted</t>
   </si>
   <si>
@@ -595,28 +598,22 @@
     <t>91 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002024X383</t>
+    <t>IN002025X026</t>
   </si>
   <si>
     <t>SOV</t>
   </si>
   <si>
-    <t>IN002024X417</t>
-  </si>
-  <si>
-    <t>IN002024X409</t>
-  </si>
-  <si>
     <t>364 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002023Z489</t>
-  </si>
-  <si>
-    <t>IN002024X425</t>
-  </si>
-  <si>
-    <t>IN002024Z040</t>
+    <t>IN002024Z115</t>
+  </si>
+  <si>
+    <t>IN002025X034</t>
+  </si>
+  <si>
+    <t>IN002025X042</t>
   </si>
   <si>
     <t>Units of Real Estate Investment Trust (REITs)</t>
@@ -640,43 +637,16 @@
     <t>Total Net Assets</t>
   </si>
   <si>
-    <t>Details of Stock Future / Index Future</t>
-  </si>
-  <si>
-    <t>Stock / Index Futures</t>
-  </si>
-  <si>
-    <t>Shree Cement Ltd. $$</t>
-  </si>
-  <si>
-    <t>FSN E-Commerce Ventures Ltd. $$</t>
-  </si>
-  <si>
-    <t>Bata India Ltd. $$</t>
-  </si>
-  <si>
-    <t>SBI Cards and Payment Services Ltd. $$</t>
-  </si>
-  <si>
-    <t>Note- 1 : Index/ Stock futures are provided towards end of the table.</t>
-  </si>
-  <si>
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
-    <t>$$ - Derivatives.</t>
-  </si>
-  <si>
-    <t>^ Value Less than 0.01% of NAV in absolute terms.</t>
-  </si>
-  <si>
     <t>For the Instrument/security whose final ISIN is yet to be assigned, disclosure of ISIN has been made as per the details provided by external agencies.</t>
   </si>
   <si>
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -695,11 +665,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="177" formatCode="##0.00"/>
     <numFmt numFmtId="178" formatCode="##0.00%"/>
-    <numFmt numFmtId="179" formatCode="\^"/>
-    <numFmt numFmtId="180" formatCode="##0"/>
+    <numFmt numFmtId="179" formatCode="##0"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -889,7 +858,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -941,7 +910,7 @@
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection/>
     </xf>
@@ -950,10 +919,6 @@
       <protection/>
     </xf>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection/>
     </xf>
@@ -1064,13 +1029,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>143</xdr:row>
+      <xdr:row>126</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>153</xdr:row>
+      <xdr:row>136</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1088,8 +1053,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="27698700"/>
-          <a:ext cx="3590925" cy="1905000"/>
+          <a:off x="666750" y="24460200"/>
+          <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -1103,13 +1068,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>158</xdr:row>
+      <xdr:row>141</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>168</xdr:row>
+      <xdr:row>151</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1127,8 +1092,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="30556200"/>
-          <a:ext cx="3590925" cy="1905000"/>
+          <a:off x="666750" y="27317700"/>
+          <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -1461,19 +1426,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J157"/>
+  <dimension ref="B1:J140"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="22" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="22" width="53.857142857142854" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="22" width="16.857142857142858" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="22" width="9.714285714285714" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="22" width="34.142857142857146" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="22" width="11.142857142857142" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="22" width="38.714285714285715" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="22" width="11.714285714285714" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="22" width="29.714285714285715" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="22" width="26.714285714285715" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="21" width="53.57142857142857" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="21" width="16.857142857142858" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="21" width="9.714285714285714" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="21" width="34.142857142857146" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="21" width="11.142857142857142" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="21" width="38.714285714285715" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="21" width="11.714285714285714" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="21" width="29.714285714285715" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="21" width="26.714285714285715" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1">
@@ -1561,10 +1526,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>2288167.47</v>
+        <v>2583814.61</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9246264820432</v>
+        <v>0.9161085368003997</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1598,10 +1563,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>2288167.47</v>
+        <v>2583814.61</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9246264820432</v>
+        <v>0.9161085368003997</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1624,13 +1589,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>11248040</v>
+        <v>16212698</v>
       </c>
       <c r="G8" s="15">
-        <v>191076.08</v>
+        <v>193287.79</v>
       </c>
       <c r="H8" s="16">
-        <v>0.077212007412</v>
+        <v>0.0685314626651</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1653,13 +1618,13 @@
         <v>17</v>
       </c>
       <c r="F9" s="14">
-        <v>16979994</v>
+        <v>8100469</v>
       </c>
       <c r="G9" s="15">
-        <v>167439.72</v>
+        <v>157546.02</v>
       </c>
       <c r="H9" s="16">
-        <v>0.0676607815154</v>
+        <v>0.0558589820271</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1679,16 +1644,16 @@
         <v>13</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F10" s="14">
-        <v>8634249</v>
+        <v>9496404</v>
       </c>
       <c r="G10" s="15">
-        <v>108169.87</v>
+        <v>134934.4</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0437104047989</v>
+        <v>0.0478418827999</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1699,25 +1664,25 @@
     </row>
     <row r="11" spans="2:10" ht="15" customHeight="1">
       <c r="B11" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D11" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F11" s="14">
-        <v>5303423</v>
+        <v>6743935</v>
       </c>
       <c r="G11" s="15">
-        <v>99693.75</v>
+        <v>113136.25</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0402852861746</v>
+        <v>0.0401132047345</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1728,25 +1693,25 @@
     </row>
     <row r="12" spans="2:10" ht="15" customHeight="1">
       <c r="B12" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F12" s="14">
-        <v>5817886</v>
+        <v>7325249</v>
       </c>
       <c r="G12" s="15">
-        <v>94616.28</v>
+        <v>105908.45</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0382335293494</v>
+        <v>0.0375505405028</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1769,13 +1734,13 @@
         <v>30</v>
       </c>
       <c r="F13" s="14">
-        <v>4943127</v>
+        <v>5602233</v>
       </c>
       <c r="G13" s="15">
-        <v>86205.66</v>
+        <v>103988.65</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0348348786456</v>
+        <v>0.036869862732</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1795,16 +1760,16 @@
         <v>13</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F14" s="14">
-        <v>8647998</v>
+        <v>6583672</v>
       </c>
       <c r="G14" s="15">
-        <v>85718.96</v>
+        <v>102883.04</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0346382078535</v>
+        <v>0.0364778614036</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1815,25 +1780,25 @@
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1">
       <c r="B15" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="F15" s="14">
-        <v>564004</v>
+        <v>12476279</v>
       </c>
       <c r="G15" s="15">
-        <v>69432.56</v>
+        <v>101344.81</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0280570301492</v>
+        <v>0.0359324717967</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1856,13 +1821,13 @@
         <v>38</v>
       </c>
       <c r="F16" s="14">
-        <v>2799748</v>
+        <v>4915426</v>
       </c>
       <c r="G16" s="15">
-        <v>69120.18</v>
+        <v>89077.35</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0279308003936</v>
+        <v>0.0315829628236</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1885,13 +1850,13 @@
         <v>41</v>
       </c>
       <c r="F17" s="14">
-        <v>10822124</v>
+        <v>624127</v>
       </c>
       <c r="G17" s="15">
-        <v>69050.56</v>
+        <v>76886.21</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0279026676208</v>
+        <v>0.0272605136107</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1911,16 +1876,16 @@
         <v>13</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F18" s="14">
-        <v>8499497</v>
+        <v>9304752</v>
       </c>
       <c r="G18" s="15">
-        <v>65692.61</v>
+        <v>72283.97</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0265457523005</v>
+        <v>0.0256287590196</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1940,16 +1905,16 @@
         <v>13</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F19" s="14">
-        <v>3279898</v>
+        <v>3516562</v>
       </c>
       <c r="G19" s="15">
-        <v>60956.90</v>
+        <v>65949.6</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0246320974065</v>
+        <v>0.0233828662958</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1969,16 +1934,16 @@
         <v>13</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F20" s="14">
-        <v>3992552</v>
+        <v>27489761</v>
       </c>
       <c r="G20" s="15">
-        <v>59233.50</v>
+        <v>65810.49</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0239356880308</v>
+        <v>0.0233335439264</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -1989,25 +1954,25 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
       <c r="B21" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D21" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F21" s="14">
-        <v>20944903</v>
+        <v>8047998</v>
       </c>
       <c r="G21" s="15">
-        <v>55003.41</v>
+        <v>65748.12</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0222263493191</v>
+        <v>0.0233114302309</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -2030,13 +1995,13 @@
         <v>53</v>
       </c>
       <c r="F22" s="14">
-        <v>16929460</v>
+        <v>1712958</v>
       </c>
       <c r="G22" s="15">
-        <v>54851.45</v>
+        <v>62952.92</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0221649437436</v>
+        <v>0.0223203736078</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -2059,13 +2024,13 @@
         <v>56</v>
       </c>
       <c r="F23" s="14">
-        <v>1475578</v>
+        <v>17208433</v>
       </c>
       <c r="G23" s="15">
-        <v>52639.77</v>
+        <v>57458.96</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0212712251131</v>
+        <v>0.0203724538007</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -2085,16 +2050,16 @@
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="F24" s="14">
-        <v>3662420</v>
+        <v>7807678</v>
       </c>
       <c r="G24" s="15">
-        <v>46333.28</v>
+        <v>56176.24</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0187228331185</v>
+        <v>0.019917656952</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -2105,25 +2070,25 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1">
       <c r="B25" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="D25" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="D25" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>62</v>
-      </c>
       <c r="F25" s="14">
-        <v>1201830</v>
+        <v>2210662</v>
       </c>
       <c r="G25" s="15">
-        <v>44042.86</v>
+        <v>51912.98</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0177972964107</v>
+        <v>0.0184060899589</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -2134,25 +2099,25 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
       <c r="B26" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="D26" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D26" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>30</v>
-      </c>
       <c r="F26" s="14">
-        <v>2595766</v>
+        <v>1140376</v>
       </c>
       <c r="G26" s="15">
-        <v>39578.94</v>
+        <v>43604.56</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0159934692434</v>
+        <v>0.0154602847684</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -2172,16 +2137,16 @@
         <v>13</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="F27" s="14">
-        <v>3192196</v>
+        <v>9895999</v>
       </c>
       <c r="G27" s="15">
-        <v>37409.34</v>
+        <v>43102.02</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0151167547364</v>
+        <v>0.015282105892</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -2192,25 +2157,25 @@
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1">
       <c r="B28" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="F28" s="14">
-        <v>704345</v>
+        <v>806674</v>
       </c>
       <c r="G28" s="15">
-        <v>35661.34</v>
+        <v>42995.72</v>
       </c>
       <c r="H28" s="16">
-        <v>0.0144104047372</v>
+        <v>0.0152444165249</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -2221,25 +2186,25 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
       <c r="B29" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F29" s="14">
-        <v>122968</v>
+        <v>1072082</v>
       </c>
       <c r="G29" s="15">
-        <v>34180.06</v>
+        <v>42905.79</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0138118337264</v>
+        <v>0.0152125312494</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -2250,25 +2215,25 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F30" s="14">
-        <v>5321771</v>
+        <v>2684881</v>
       </c>
       <c r="G30" s="15">
-        <v>32130.19</v>
+        <v>42652.02</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0129835009616</v>
+        <v>0.0151225554196</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -2279,25 +2244,25 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="F31" s="14">
-        <v>402647</v>
+        <v>3632304</v>
       </c>
       <c r="G31" s="15">
-        <v>31099.25</v>
+        <v>41691.59</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0125669080164</v>
+        <v>0.0147820286192</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -2308,25 +2273,25 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
       <c r="B32" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D32" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="F32" s="14">
-        <v>3368237</v>
+        <v>3041363</v>
       </c>
       <c r="G32" s="15">
-        <v>30903.57</v>
+        <v>38053.53</v>
       </c>
       <c r="H32" s="16">
-        <v>0.0124878356092</v>
+        <v>0.0134921304158</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2337,25 +2302,25 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1">
       <c r="B33" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F33" s="14">
-        <v>6783170</v>
+        <v>1221854</v>
       </c>
       <c r="G33" s="15">
-        <v>30354.69</v>
+        <v>36372.15</v>
       </c>
       <c r="H33" s="16">
-        <v>0.0122660384767</v>
+        <v>0.0128959860308</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2366,25 +2331,25 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
       <c r="B34" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D34" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="F34" s="14">
-        <v>1686030</v>
+        <v>704345</v>
       </c>
       <c r="G34" s="15">
-        <v>27843.10</v>
+        <v>35911.03</v>
       </c>
       <c r="H34" s="16">
-        <v>0.0112511290977</v>
+        <v>0.012732492889</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2395,25 +2360,25 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
       <c r="B35" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="F35" s="14">
-        <v>795769</v>
+        <v>15522000</v>
       </c>
       <c r="G35" s="15">
-        <v>27722.60</v>
+        <v>31129.37</v>
       </c>
       <c r="H35" s="16">
-        <v>0.0112024362059</v>
+        <v>0.0110371237518</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2424,25 +2389,25 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
       <c r="B36" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D36" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="F36" s="14">
-        <v>15657089</v>
+        <v>6152964</v>
       </c>
       <c r="G36" s="15">
-        <v>27337.28</v>
+        <v>29389.63</v>
       </c>
       <c r="H36" s="16">
-        <v>0.0110467320974</v>
+        <v>0.0104202874433</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2453,25 +2418,25 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
       <c r="B37" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D37" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="F37" s="14">
-        <v>1643412</v>
+        <v>6986586</v>
       </c>
       <c r="G37" s="15">
-        <v>24781.83</v>
+        <v>29207.42</v>
       </c>
       <c r="H37" s="16">
-        <v>0.0100140993139</v>
+        <v>0.0103556836842</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -2491,16 +2456,16 @@
         <v>13</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="F38" s="14">
-        <v>3459507</v>
+        <v>2013235</v>
       </c>
       <c r="G38" s="15">
-        <v>24773.53</v>
+        <v>28738.93</v>
       </c>
       <c r="H38" s="16">
-        <v>0.0100107453637</v>
+        <v>0.0101895774602</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>13</v>
@@ -2523,13 +2488,13 @@
         <v>95</v>
       </c>
       <c r="F39" s="14">
-        <v>18132117</v>
+        <v>1636979</v>
       </c>
       <c r="G39" s="15">
-        <v>24409.46</v>
+        <v>28411.41</v>
       </c>
       <c r="H39" s="16">
-        <v>0.0098636281759</v>
+        <v>0.0100734530809</v>
       </c>
       <c r="I39" s="15" t="s">
         <v>13</v>
@@ -2549,16 +2514,16 @@
         <v>13</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="F40" s="14">
-        <v>3919187</v>
+        <v>3160775</v>
       </c>
       <c r="G40" s="15">
-        <v>24142.19</v>
+        <v>28040.82</v>
       </c>
       <c r="H40" s="16">
-        <v>0.0097556269378</v>
+        <v>0.0099420579485</v>
       </c>
       <c r="I40" s="15" t="s">
         <v>13</v>
@@ -2569,25 +2534,25 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
       <c r="B41" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D41" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="F41" s="14">
-        <v>13840455</v>
+        <v>3919187</v>
       </c>
       <c r="G41" s="15">
-        <v>23376.53</v>
+        <v>25960.69</v>
       </c>
       <c r="H41" s="16">
-        <v>0.0094462310909</v>
+        <v>0.0092045341172</v>
       </c>
       <c r="I41" s="15" t="s">
         <v>13</v>
@@ -2598,25 +2563,25 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
       <c r="B42" s="12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D42" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F42" s="14">
-        <v>2248909</v>
+        <v>983164</v>
       </c>
       <c r="G42" s="15">
-        <v>22176.49</v>
+        <v>24305.78</v>
       </c>
       <c r="H42" s="16">
-        <v>0.008961306461</v>
+        <v>0.0086177748455</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>13</v>
@@ -2627,25 +2592,25 @@
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1">
       <c r="B43" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D43" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F43" s="14">
-        <v>2089417</v>
+        <v>2086043</v>
       </c>
       <c r="G43" s="15">
-        <v>22119.61</v>
+        <v>23754.81</v>
       </c>
       <c r="H43" s="16">
-        <v>0.0089383217997</v>
+        <v>0.0084224247927</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>13</v>
@@ -2656,25 +2621,25 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1">
       <c r="B44" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D44" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="F44" s="14">
-        <v>2589921</v>
+        <v>2303921</v>
       </c>
       <c r="G44" s="15">
-        <v>20500.52</v>
+        <v>21861.91</v>
       </c>
       <c r="H44" s="16">
-        <v>0.0082840630925</v>
+        <v>0.0077512845946</v>
       </c>
       <c r="I44" s="15" t="s">
         <v>13</v>
@@ -2685,25 +2650,25 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
       <c r="B45" s="12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D45" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="F45" s="14">
-        <v>833619</v>
+        <v>3472867</v>
       </c>
       <c r="G45" s="15">
-        <v>20489.52</v>
+        <v>21806.13</v>
       </c>
       <c r="H45" s="16">
-        <v>0.0082796180982</v>
+        <v>0.0077315074271</v>
       </c>
       <c r="I45" s="15" t="s">
         <v>13</v>
@@ -2714,25 +2679,25 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
       <c r="B46" s="12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D46" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>111</v>
+        <v>25</v>
       </c>
       <c r="F46" s="14">
-        <v>5854388</v>
+        <v>2280577</v>
       </c>
       <c r="G46" s="15">
-        <v>20238.62</v>
+        <v>21209.37</v>
       </c>
       <c r="H46" s="16">
-        <v>0.0081782318197</v>
+        <v>0.0075199222274</v>
       </c>
       <c r="I46" s="15" t="s">
         <v>13</v>
@@ -2743,25 +2708,25 @@
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1">
       <c r="B47" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D47" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>41</v>
+        <v>115</v>
       </c>
       <c r="F47" s="14">
-        <v>4006628</v>
+        <v>5781196</v>
       </c>
       <c r="G47" s="15">
-        <v>17358.72</v>
+        <v>19008.57</v>
       </c>
       <c r="H47" s="16">
-        <v>0.0070144919097</v>
+        <v>0.0067396140504</v>
       </c>
       <c r="I47" s="15" t="s">
         <v>13</v>
@@ -2772,25 +2737,25 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
       <c r="B48" s="12" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D48" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="F48" s="14">
-        <v>930057</v>
+        <v>971786</v>
       </c>
       <c r="G48" s="15">
-        <v>17358.12</v>
+        <v>16289.08</v>
       </c>
       <c r="H48" s="16">
-        <v>0.0070142494555</v>
+        <v>0.0057754009079</v>
       </c>
       <c r="I48" s="15" t="s">
         <v>13</v>
@@ -2801,25 +2766,25 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
       <c r="B49" s="12" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D49" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="F49" s="14">
-        <v>1992923</v>
+        <v>1180821</v>
       </c>
       <c r="G49" s="15">
-        <v>15508.93</v>
+        <v>14652.81</v>
       </c>
       <c r="H49" s="16">
-        <v>0.0062670095498</v>
+        <v>0.0051952505714</v>
       </c>
       <c r="I49" s="15" t="s">
         <v>13</v>
@@ -2830,25 +2795,25 @@
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
       <c r="B50" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D50" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F50" s="14">
-        <v>1136908</v>
+        <v>8659895</v>
       </c>
       <c r="G50" s="15">
-        <v>13916.32</v>
+        <v>13944.16</v>
       </c>
       <c r="H50" s="16">
-        <v>0.0056234511561</v>
+        <v>0.0049439940331</v>
       </c>
       <c r="I50" s="15" t="s">
         <v>13</v>
@@ -2868,16 +2833,16 @@
         <v>13</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>121</v>
+        <v>48</v>
       </c>
       <c r="F51" s="14">
-        <v>483164</v>
+        <v>3127641</v>
       </c>
       <c r="G51" s="15">
-        <v>13389.68</v>
+        <v>13348.77</v>
       </c>
       <c r="H51" s="16">
-        <v>0.0054106409939</v>
+        <v>0.0047328945759</v>
       </c>
       <c r="I51" s="15" t="s">
         <v>13</v>
@@ -2897,16 +2862,16 @@
         <v>13</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="F52" s="14">
-        <v>1307398</v>
+        <v>2804382</v>
       </c>
       <c r="G52" s="15">
-        <v>12685.03</v>
+        <v>13159.56</v>
       </c>
       <c r="H52" s="16">
-        <v>0.0051258987016</v>
+        <v>0.0046658089206</v>
       </c>
       <c r="I52" s="15" t="s">
         <v>13</v>
@@ -2926,16 +2891,16 @@
         <v>13</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="F53" s="14">
-        <v>2804382</v>
+        <v>826990</v>
       </c>
       <c r="G53" s="15">
-        <v>12471.09</v>
+        <v>10789.74</v>
       </c>
       <c r="H53" s="16">
-        <v>0.0050394476038</v>
+        <v>0.0038255735862</v>
       </c>
       <c r="I53" s="15" t="s">
         <v>13</v>
@@ -2946,25 +2911,25 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1">
       <c r="B54" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D54" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="F54" s="14">
         <v>2265432</v>
       </c>
       <c r="G54" s="15">
-        <v>10521.80</v>
+        <v>10188.78</v>
       </c>
       <c r="H54" s="16">
-        <v>0.0042517582503</v>
+        <v>0.0036124992487</v>
       </c>
       <c r="I54" s="15" t="s">
         <v>13</v>
@@ -2975,25 +2940,25 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1">
       <c r="B55" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D55" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F55" s="14">
-        <v>1055237</v>
+        <v>1518132</v>
       </c>
       <c r="G55" s="15">
-        <v>10383.53</v>
+        <v>9815.48</v>
       </c>
       <c r="H55" s="16">
-        <v>0.0041958846723</v>
+        <v>0.003480143268</v>
       </c>
       <c r="I55" s="15" t="s">
         <v>13</v>
@@ -3004,25 +2969,25 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1">
       <c r="B56" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D56" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>135</v>
+        <v>70</v>
       </c>
       <c r="F56" s="14">
-        <v>735371</v>
+        <v>1033356</v>
       </c>
       <c r="G56" s="15">
-        <v>9536.29</v>
+        <v>9618.48</v>
       </c>
       <c r="H56" s="16">
-        <v>0.0038535231315</v>
+        <v>0.0034102956167</v>
       </c>
       <c r="I56" s="15" t="s">
         <v>13</v>
@@ -3042,16 +3007,16 @@
         <v>13</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F57" s="14">
-        <v>651216</v>
+        <v>667726</v>
       </c>
       <c r="G57" s="15">
-        <v>9471.61</v>
+        <v>8992.93</v>
       </c>
       <c r="H57" s="16">
-        <v>0.0038273865652</v>
+        <v>0.0031885027323</v>
       </c>
       <c r="I57" s="15" t="s">
         <v>13</v>
@@ -3071,16 +3036,16 @@
         <v>13</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="F58" s="14">
-        <v>2960036</v>
+        <v>1875486</v>
       </c>
       <c r="G58" s="15">
-        <v>9442.51</v>
+        <v>7960.50</v>
       </c>
       <c r="H58" s="16">
-        <v>0.0038156275348</v>
+        <v>0.0028224478563</v>
       </c>
       <c r="I58" s="15" t="s">
         <v>13</v>
@@ -3100,16 +3065,16 @@
         <v>13</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="F59" s="14">
-        <v>1875486</v>
+        <v>2607144</v>
       </c>
       <c r="G59" s="15">
-        <v>8901.06</v>
+        <v>7611.56</v>
       </c>
       <c r="H59" s="16">
-        <v>0.003596832794</v>
+        <v>0.0026987288745</v>
       </c>
       <c r="I59" s="15" t="s">
         <v>13</v>
@@ -3129,16 +3094,16 @@
         <v>13</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>132</v>
+        <v>22</v>
       </c>
       <c r="F60" s="14">
-        <v>196529</v>
+        <v>2248865</v>
       </c>
       <c r="G60" s="15">
-        <v>8498.60</v>
+        <v>7160.39</v>
       </c>
       <c r="H60" s="16">
-        <v>0.0034342025762</v>
+        <v>0.0025387635709</v>
       </c>
       <c r="I60" s="15" t="s">
         <v>13</v>
@@ -3158,16 +3123,16 @@
         <v>13</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="F61" s="14">
-        <v>2020060</v>
+        <v>2984360</v>
       </c>
       <c r="G61" s="15">
-        <v>8493.34</v>
+        <v>7112.03</v>
       </c>
       <c r="H61" s="16">
-        <v>0.0034320770607</v>
+        <v>0.0025216172134</v>
       </c>
       <c r="I61" s="15" t="s">
         <v>13</v>
@@ -3187,16 +3152,16 @@
         <v>13</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F62" s="14">
-        <v>1537225</v>
+        <v>715753</v>
       </c>
       <c r="G62" s="15">
-        <v>7882.89</v>
+        <v>6917.04</v>
       </c>
       <c r="H62" s="16">
-        <v>0.003185400083</v>
+        <v>0.002452482221</v>
       </c>
       <c r="I62" s="15" t="s">
         <v>13</v>
@@ -3216,16 +3181,16 @@
         <v>13</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="F63" s="14">
-        <v>1072741</v>
+        <v>437040</v>
       </c>
       <c r="G63" s="15">
-        <v>7759.67</v>
+        <v>6787.23</v>
       </c>
       <c r="H63" s="16">
-        <v>0.0031356080654</v>
+        <v>0.002406457228</v>
       </c>
       <c r="I63" s="15" t="s">
         <v>13</v>
@@ -3245,16 +3210,16 @@
         <v>13</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>62</v>
+        <v>152</v>
       </c>
       <c r="F64" s="14">
-        <v>3384360</v>
+        <v>122117</v>
       </c>
       <c r="G64" s="15">
-        <v>7457.44</v>
+        <v>6729.26</v>
       </c>
       <c r="H64" s="16">
-        <v>0.0030134798272</v>
+        <v>0.0023859035816</v>
       </c>
       <c r="I64" s="15" t="s">
         <v>13</v>
@@ -3265,25 +3230,25 @@
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1">
       <c r="B65" s="12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D65" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F65" s="14">
-        <v>787808</v>
+        <v>497871</v>
       </c>
       <c r="G65" s="15">
-        <v>5882.17</v>
+        <v>6292.09</v>
       </c>
       <c r="H65" s="16">
-        <v>0.0023769283608</v>
+        <v>0.0022309020705</v>
       </c>
       <c r="I65" s="15" t="s">
         <v>13</v>
@@ -3294,25 +3259,25 @@
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1">
       <c r="B66" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D66" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>154</v>
+        <v>103</v>
       </c>
       <c r="F66" s="14">
-        <v>654898</v>
+        <v>1098669</v>
       </c>
       <c r="G66" s="15">
-        <v>5227.72</v>
+        <v>5169.79</v>
       </c>
       <c r="H66" s="16">
-        <v>0.002112471406</v>
+        <v>0.0018329831924</v>
       </c>
       <c r="I66" s="15" t="s">
         <v>13</v>
@@ -3323,25 +3288,25 @@
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1">
       <c r="B67" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D67" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F67" s="14">
-        <v>462302</v>
+        <v>1269986</v>
       </c>
       <c r="G67" s="15">
-        <v>5041.4</v>
+        <v>5109.15</v>
       </c>
       <c r="H67" s="16">
-        <v>0.0020371812848</v>
+        <v>0.0018114828798</v>
       </c>
       <c r="I67" s="15" t="s">
         <v>13</v>
@@ -3352,25 +3317,25 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
       <c r="B68" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D68" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>30</v>
+        <v>133</v>
       </c>
       <c r="F68" s="14">
-        <v>197034</v>
+        <v>435006</v>
       </c>
       <c r="G68" s="15">
-        <v>2914.92</v>
+        <v>4564.08</v>
       </c>
       <c r="H68" s="16">
-        <v>0.0011778911554</v>
+        <v>0.001618224711</v>
       </c>
       <c r="I68" s="15" t="s">
         <v>13</v>
@@ -3381,25 +3346,25 @@
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1">
       <c r="B69" s="12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D69" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>74</v>
+        <v>165</v>
       </c>
       <c r="F69" s="14">
-        <v>845671</v>
+        <v>462302</v>
       </c>
       <c r="G69" s="15">
-        <v>2225.81</v>
+        <v>4554.83</v>
       </c>
       <c r="H69" s="16">
-        <v>0.0008994284277</v>
+        <v>0.0016149450624</v>
       </c>
       <c r="I69" s="15" t="s">
         <v>13</v>
@@ -3410,25 +3375,25 @@
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1">
       <c r="B70" s="12" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D70" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>166</v>
+        <v>64</v>
       </c>
       <c r="F70" s="14">
-        <v>51053</v>
+        <v>845671</v>
       </c>
       <c r="G70" s="15">
-        <v>1879.06</v>
+        <v>3465.98</v>
       </c>
       <c r="H70" s="16">
-        <v>0.0007593100855</v>
+        <v>0.0012288861027</v>
       </c>
       <c r="I70" s="15" t="s">
         <v>13</v>
@@ -3439,25 +3404,25 @@
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1">
       <c r="B71" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D71" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="F71" s="14">
-        <v>131282</v>
+        <v>50106</v>
       </c>
       <c r="G71" s="15">
-        <v>919.76</v>
+        <v>1752.66</v>
       </c>
       <c r="H71" s="16">
-        <v>0.0003716661757</v>
+        <v>0.0006214171798</v>
       </c>
       <c r="I71" s="15" t="s">
         <v>13</v>
@@ -3468,25 +3433,25 @@
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1">
       <c r="B72" s="12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D72" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>71</v>
+        <v>173</v>
       </c>
       <c r="F72" s="14">
-        <v>264970</v>
+        <v>514770</v>
       </c>
       <c r="G72" s="15">
-        <v>699.79</v>
+        <v>1632.59</v>
       </c>
       <c r="H72" s="16">
-        <v>0.000282778413</v>
+        <v>0.0005788455682</v>
       </c>
       <c r="I72" s="15" t="s">
         <v>13</v>
@@ -3497,25 +3462,25 @@
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1">
       <c r="B73" s="12" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D73" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>173</v>
+        <v>53</v>
       </c>
       <c r="F73" s="14">
-        <v>406048</v>
+        <v>2394705</v>
       </c>
       <c r="G73" s="15">
-        <v>661.66</v>
+        <v>1227.77</v>
       </c>
       <c r="H73" s="16">
-        <v>0.0002673704464</v>
+        <v>0.0004353139632</v>
       </c>
       <c r="I73" s="15" t="s">
         <v>13</v>
@@ -3526,25 +3491,25 @@
     </row>
     <row r="74" spans="2:10" ht="15" customHeight="1">
       <c r="B74" s="12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D74" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="F74" s="14">
-        <v>110016</v>
+        <v>397454</v>
       </c>
       <c r="G74" s="15">
-        <v>534.68</v>
+        <v>807.87</v>
       </c>
       <c r="H74" s="16">
-        <v>0.0002160590489</v>
+        <v>0.0002864356447</v>
       </c>
       <c r="I74" s="15" t="s">
         <v>13</v>
@@ -3555,25 +3520,25 @@
     </row>
     <row r="75" spans="2:10" ht="15" customHeight="1">
       <c r="B75" s="12" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D75" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>17</v>
+        <v>115</v>
       </c>
       <c r="F75" s="14">
-        <v>27112</v>
+        <v>110016</v>
       </c>
       <c r="G75" s="15">
-        <v>515.48</v>
+        <v>506.13</v>
       </c>
       <c r="H75" s="16">
-        <v>0.0002083005134</v>
+        <v>0.0001794517346</v>
       </c>
       <c r="I75" s="15" t="s">
         <v>13</v>
@@ -3584,25 +3549,25 @@
     </row>
     <row r="76" spans="2:10" ht="15" customHeight="1">
       <c r="B76" s="12" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D76" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>71</v>
+        <v>155</v>
       </c>
       <c r="F76" s="14">
-        <v>10478</v>
+        <v>37043</v>
       </c>
       <c r="G76" s="15">
-        <v>122.33</v>
-      </c>
-      <c r="H76" s="17" t="s">
-        <v>180</v>
+        <v>254.37</v>
+      </c>
+      <c r="H76" s="16">
+        <v>0.0000901885636</v>
       </c>
       <c r="I76" s="15" t="s">
         <v>13</v>
@@ -3621,7 +3586,7 @@
     </row>
     <row r="78" spans="2:10" ht="15" customHeight="1">
       <c r="B78" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C78" s="8" t="s">
         <v>13</v>
@@ -3636,10 +3601,10 @@
         <v>13</v>
       </c>
       <c r="G78" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H78" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I78" s="9" t="s">
         <v>13</v>
@@ -3658,25 +3623,25 @@
     </row>
     <row r="80" spans="2:10" ht="15" customHeight="1">
       <c r="B80" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G80" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="C80" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E80" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F80" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G80" s="9" t="s">
-        <v>182</v>
-      </c>
       <c r="H80" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I80" s="9" t="s">
         <v>13</v>
@@ -3710,10 +3675,10 @@
         <v>13</v>
       </c>
       <c r="G82" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H82" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I82" s="9" t="s">
         <v>13</v>
@@ -3732,7 +3697,7 @@
     </row>
     <row r="84" spans="2:10" ht="15" customHeight="1">
       <c r="B84" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>13</v>
@@ -3747,10 +3712,10 @@
         <v>13</v>
       </c>
       <c r="G84" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H84" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I84" s="9" t="s">
         <v>13</v>
@@ -3769,7 +3734,7 @@
     </row>
     <row r="86" spans="2:10" ht="15" customHeight="1">
       <c r="B86" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C86" s="8" t="s">
         <v>13</v>
@@ -3784,10 +3749,10 @@
         <v>13</v>
       </c>
       <c r="G86" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H86" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I86" s="9" t="s">
         <v>13</v>
@@ -3806,7 +3771,7 @@
     </row>
     <row r="88" spans="2:10" ht="15" customHeight="1">
       <c r="B88" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C88" s="8" t="s">
         <v>13</v>
@@ -3821,10 +3786,10 @@
         <v>13</v>
       </c>
       <c r="G88" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H88" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I88" s="9" t="s">
         <v>13</v>
@@ -3843,7 +3808,7 @@
     </row>
     <row r="90" spans="2:10" ht="15" customHeight="1">
       <c r="B90" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C90" s="8" t="s">
         <v>13</v>
@@ -3858,10 +3823,10 @@
         <v>13</v>
       </c>
       <c r="G90" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H90" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I90" s="9" t="s">
         <v>13</v>
@@ -3880,7 +3845,7 @@
     </row>
     <row r="92" spans="2:10" ht="15" customHeight="1">
       <c r="B92" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C92" s="8" t="s">
         <v>13</v>
@@ -3895,10 +3860,10 @@
         <v>13</v>
       </c>
       <c r="G92" s="9">
-        <v>54169.89</v>
+        <v>26352.69</v>
       </c>
       <c r="H92" s="10">
-        <v>0.0218895318982</v>
+        <v>0.0093435203064</v>
       </c>
       <c r="I92" s="9" t="s">
         <v>13</v>
@@ -3917,7 +3882,7 @@
     </row>
     <row r="94" spans="2:10" ht="15" customHeight="1">
       <c r="B94" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C94" s="8" t="s">
         <v>13</v>
@@ -3932,10 +3897,10 @@
         <v>13</v>
       </c>
       <c r="G94" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H94" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I94" s="9" t="s">
         <v>13</v>
@@ -3954,7 +3919,7 @@
     </row>
     <row r="96" spans="2:10" ht="15" customHeight="1">
       <c r="B96" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>13</v>
@@ -3969,10 +3934,10 @@
         <v>13</v>
       </c>
       <c r="G96" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H96" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I96" s="9" t="s">
         <v>13</v>
@@ -3991,7 +3956,7 @@
     </row>
     <row r="98" spans="2:10" ht="15" customHeight="1">
       <c r="B98" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>13</v>
@@ -4006,10 +3971,10 @@
         <v>13</v>
       </c>
       <c r="G98" s="9">
-        <v>54169.89</v>
+        <v>26352.69</v>
       </c>
       <c r="H98" s="10">
-        <v>0.0218895318982</v>
+        <v>0.0093435203064</v>
       </c>
       <c r="I98" s="9" t="s">
         <v>13</v>
@@ -4020,28 +3985,28 @@
     </row>
     <row r="99" spans="2:10" ht="15" customHeight="1">
       <c r="B99" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C99" s="13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D99" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F99" s="14">
-        <v>20000000</v>
+        <v>15000000</v>
       </c>
       <c r="G99" s="15">
-        <v>19808.22</v>
+        <v>14908.50</v>
       </c>
       <c r="H99" s="16">
-        <v>0.0080043113165</v>
+        <v>0.0052859071498</v>
       </c>
       <c r="I99" s="15">
-        <v>6.43</v>
+        <v>5.60</v>
       </c>
       <c r="J99" s="11" t="s">
         <v>13</v>
@@ -4049,28 +4014,28 @@
     </row>
     <row r="100" spans="2:10" ht="15" customHeight="1">
       <c r="B100" s="12" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C100" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="D100" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E100" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="D100" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E100" s="13" t="s">
-        <v>194</v>
-      </c>
       <c r="F100" s="14">
-        <v>15150000</v>
+        <v>5000000</v>
       </c>
       <c r="G100" s="15">
-        <v>14949.79</v>
+        <v>4991.43</v>
       </c>
       <c r="H100" s="16">
-        <v>0.00604106645</v>
+        <v>0.0017697444763</v>
       </c>
       <c r="I100" s="15">
-        <v>6.52</v>
+        <v>5.70</v>
       </c>
       <c r="J100" s="11" t="s">
         <v>13</v>
@@ -4078,28 +4043,28 @@
     </row>
     <row r="101" spans="2:10" ht="15" customHeight="1">
       <c r="B101" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C101" s="13" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D101" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F101" s="14">
-        <v>11600000</v>
+        <v>5000000</v>
       </c>
       <c r="G101" s="15">
-        <v>11460.75</v>
+        <v>4964.89</v>
       </c>
       <c r="H101" s="16">
-        <v>0.0046311789207</v>
+        <v>0.001760334544</v>
       </c>
       <c r="I101" s="15">
-        <v>6.52</v>
+        <v>5.61</v>
       </c>
       <c r="J101" s="11" t="s">
         <v>13</v>
@@ -4107,28 +4072,28 @@
     </row>
     <row r="102" spans="2:10" ht="15" customHeight="1">
       <c r="B102" s="12" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C102" s="13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D102" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F102" s="14">
-        <v>5400000</v>
+        <v>1500000</v>
       </c>
       <c r="G102" s="15">
-        <v>5388.62</v>
+        <v>1487.87</v>
       </c>
       <c r="H102" s="16">
-        <v>0.0021774895496</v>
+        <v>0.0005275341363</v>
       </c>
       <c r="I102" s="15">
-        <v>6.42</v>
+        <v>5.61</v>
       </c>
       <c r="J102" s="11" t="s">
         <v>13</v>
@@ -4136,57 +4101,36 @@
     </row>
     <row r="103" spans="2:10" ht="15" customHeight="1">
       <c r="B103" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="C103" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="D103" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E103" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="F103" s="14">
-        <v>2500000</v>
-      </c>
-      <c r="G103" s="15">
-        <v>2463.95</v>
-      </c>
-      <c r="H103" s="16">
-        <v>0.0009956585128</v>
-      </c>
-      <c r="I103" s="15">
-        <v>6.51</v>
+        <v>13</v>
       </c>
       <c r="J103" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="104" spans="2:10" ht="15" customHeight="1">
-      <c r="B104" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="C104" s="13" t="s">
+      <c r="B104" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="D104" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E104" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="F104" s="14">
-        <v>100000</v>
-      </c>
-      <c r="G104" s="15">
-        <v>98.56</v>
-      </c>
-      <c r="H104" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="I104" s="15">
-        <v>6.51</v>
+      <c r="C104" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D104" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E104" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F104" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G104" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="H104" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="I104" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J104" s="11" t="s">
         <v>13</v>
@@ -4217,10 +4161,10 @@
         <v>13</v>
       </c>
       <c r="G106" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H106" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I106" s="9" t="s">
         <v>13</v>
@@ -4253,11 +4197,11 @@
       <c r="F108" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G108" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="H108" s="10" t="s">
-        <v>182</v>
+      <c r="G108" s="9">
+        <v>209083.71</v>
+      </c>
+      <c r="H108" s="10">
+        <v>0.0741320104377</v>
       </c>
       <c r="I108" s="9" t="s">
         <v>13</v>
@@ -4291,10 +4235,10 @@
         <v>13</v>
       </c>
       <c r="G110" s="9">
-        <v>128702.18</v>
+        <v>5016.0004934</v>
       </c>
       <c r="H110" s="10">
-        <v>0.0520073139249</v>
+        <v>0.001778456107</v>
       </c>
       <c r="I110" s="9" t="s">
         <v>13</v>
@@ -4305,6 +4249,20 @@
     </row>
     <row r="111" spans="2:10" ht="15" customHeight="1">
       <c r="B111" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C111" s="13"/>
+      <c r="D111" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E111" s="13"/>
+      <c r="G111" s="15">
+        <v>5016.0004934</v>
+      </c>
+      <c r="H111" s="16">
+        <v>0.001778456107</v>
+      </c>
+      <c r="I111" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J111" s="11" t="s">
@@ -4312,28 +4270,7 @@
       </c>
     </row>
     <row r="112" spans="2:10" ht="15" customHeight="1">
-      <c r="B112" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C112" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D112" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E112" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F112" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G112" s="9">
-        <v>7876.000493400001</v>
-      </c>
-      <c r="H112" s="10">
-        <v>0.0031826160996</v>
-      </c>
-      <c r="I112" s="9" t="s">
+      <c r="B112" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J112" s="11" t="s">
@@ -4341,388 +4278,144 @@
       </c>
     </row>
     <row r="113" spans="2:10" ht="15" customHeight="1">
-      <c r="B113" s="12" t="s">
+      <c r="B113" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="C113" s="13"/>
-      <c r="D113" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E113" s="13"/>
-      <c r="G113" s="15">
-        <v>7876.000493400001</v>
-      </c>
-      <c r="H113" s="16">
-        <v>0.0031826160996</v>
-      </c>
-      <c r="I113" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J113" s="11" t="s">
+      <c r="C113" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D113" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E113" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F113" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G113" s="18">
+        <v>-3842.8945756303146</v>
+      </c>
+      <c r="H113" s="19">
+        <v>-0.0013625236551985129</v>
+      </c>
+      <c r="I113" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J113" s="20" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="114" spans="2:10" ht="15" customHeight="1">
-      <c r="B114" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J114" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="115" spans="2:10" ht="15" customHeight="1">
-      <c r="B115" s="18" t="s">
+      <c r="B114" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="C115" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D115" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E115" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F115" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G115" s="19">
-        <v>-4221.689053579699</v>
-      </c>
-      <c r="H115" s="20">
-        <v>-0.0017059439700484352</v>
-      </c>
-      <c r="I115" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J115" s="21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="116" spans="2:10" ht="15" customHeight="1">
-      <c r="B116" s="18" t="s">
+      <c r="C114" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D114" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E114" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F114" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G114" s="18">
+        <v>2820424.11591777</v>
+      </c>
+      <c r="H114" s="19">
+        <v>0.9999999999963017</v>
+      </c>
+      <c r="I114" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J114" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="117" spans="2:9" ht="15" customHeight="1">
+      <c r="B117" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="C116" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D116" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E116" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F116" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G116" s="19">
-        <v>2474693.85143982</v>
-      </c>
-      <c r="H116" s="20">
-        <v>0.9999999999958515</v>
-      </c>
-      <c r="I116" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J116" s="21" t="s">
-        <v>13</v>
-      </c>
+      <c r="C117" s="21"/>
+      <c r="D117" s="21"/>
+      <c r="E117" s="21"/>
+      <c r="F117" s="21"/>
+      <c r="G117" s="21"/>
+      <c r="H117" s="21"/>
+      <c r="I117" s="21"/>
     </row>
     <row r="118" spans="2:8" ht="15" customHeight="1">
-      <c r="B118" s="19" t="s">
+      <c r="B118" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="C118" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D118" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E118" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F118" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G118" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="H118" s="19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="119" spans="2:8" ht="15" customHeight="1">
-      <c r="B119" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C119" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D119" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="E119" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F119" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G119" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="H119" s="19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="120" spans="2:8" ht="15" customHeight="1">
-      <c r="B120" s="7" t="s">
+      <c r="C118" s="21"/>
+      <c r="D118" s="21"/>
+      <c r="E118" s="21"/>
+      <c r="F118" s="21"/>
+      <c r="G118" s="21"/>
+      <c r="H118" s="21"/>
+    </row>
+    <row r="119" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B119" s="22" t="s">
         <v>209</v>
       </c>
-      <c r="C120" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D120" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E120" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F120" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G120" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H120" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="121" spans="2:10" ht="15" customHeight="1">
-      <c r="B121" s="12" t="s">
+      <c r="C119" s="21"/>
+      <c r="D119" s="21"/>
+      <c r="E119" s="21"/>
+      <c r="F119" s="21"/>
+      <c r="G119" s="21"/>
+      <c r="H119" s="21"/>
+    </row>
+    <row r="120" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B120" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="C121" s="13"/>
-      <c r="D121" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E121" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="F121" s="14">
-        <v>22075</v>
-      </c>
-      <c r="G121" s="15">
-        <v>6092.48</v>
-      </c>
-      <c r="H121" s="16">
-        <v>0.0024619126105</v>
-      </c>
-      <c r="I121" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J121" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="122" spans="2:10" ht="15" customHeight="1">
-      <c r="B122" s="12" t="s">
+      <c r="C120" s="21"/>
+      <c r="D120" s="21"/>
+      <c r="E120" s="21"/>
+      <c r="F120" s="21"/>
+      <c r="G120" s="21"/>
+      <c r="H120" s="21"/>
+    </row>
+    <row r="121" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B121" s="22" t="s">
         <v>211</v>
       </c>
-      <c r="C122" s="13"/>
-      <c r="D122" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E122" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="F122" s="14">
-        <v>2492750</v>
-      </c>
-      <c r="G122" s="15">
-        <v>4188.07</v>
-      </c>
-      <c r="H122" s="16">
-        <v>0.0016923588336</v>
-      </c>
-      <c r="I122" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J122" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="123" spans="2:10" ht="15" customHeight="1">
-      <c r="B123" s="12" t="s">
+      <c r="C121" s="21"/>
+      <c r="D121" s="21"/>
+      <c r="E121" s="21"/>
+      <c r="F121" s="21"/>
+      <c r="G121" s="21"/>
+      <c r="H121" s="21"/>
+    </row>
+    <row r="124" ht="15">
+      <c r="B124" s="21" t="s">
         <v>212</v>
       </c>
-      <c r="C123" s="13"/>
-      <c r="D123" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E123" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="F123" s="14">
-        <v>73125</v>
-      </c>
-      <c r="G123" s="15">
-        <v>952.27</v>
-      </c>
-      <c r="H123" s="16">
-        <v>0.0003848031543</v>
-      </c>
-      <c r="I123" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J123" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="124" spans="2:10" ht="15" customHeight="1">
-      <c r="B124" s="12" t="s">
+    </row>
+    <row r="139" ht="15">
+      <c r="B139" s="21" t="s">
         <v>213</v>
       </c>
-      <c r="C124" s="13"/>
-      <c r="D124" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E124" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="F124" s="14">
-        <v>72800</v>
-      </c>
-      <c r="G124" s="15">
-        <v>567.59</v>
-      </c>
-      <c r="H124" s="16">
-        <v>0.0002293576636</v>
-      </c>
-      <c r="I124" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J124" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="128" spans="2:9" ht="15" customHeight="1">
-      <c r="B128" s="13" t="s">
+    </row>
+    <row r="140" ht="15">
+      <c r="B140" s="21" t="s">
         <v>214</v>
       </c>
-      <c r="C128" s="22"/>
-      <c r="D128" s="22"/>
-      <c r="E128" s="22"/>
-      <c r="F128" s="22"/>
-      <c r="G128" s="22"/>
-      <c r="H128" s="22"/>
-      <c r="I128" s="22"/>
-    </row>
-    <row r="132" spans="2:9" ht="15" customHeight="1">
-      <c r="B132" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="C132" s="22"/>
-      <c r="D132" s="22"/>
-      <c r="E132" s="22"/>
-      <c r="F132" s="22"/>
-      <c r="G132" s="22"/>
-      <c r="H132" s="22"/>
-      <c r="I132" s="22"/>
-    </row>
-    <row r="133" spans="2:8" ht="15" customHeight="1">
-      <c r="B133" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="C133" s="22"/>
-      <c r="D133" s="22"/>
-      <c r="E133" s="22"/>
-      <c r="F133" s="22"/>
-      <c r="G133" s="22"/>
-      <c r="H133" s="22"/>
-    </row>
-    <row r="134" spans="2:8" ht="15" customHeight="1">
-      <c r="B134" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="C134" s="22"/>
-      <c r="D134" s="22"/>
-      <c r="E134" s="22"/>
-      <c r="F134" s="22"/>
-      <c r="G134" s="22"/>
-      <c r="H134" s="22"/>
-    </row>
-    <row r="135" spans="2:8" ht="15" customHeight="1">
-      <c r="B135" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="C135" s="22"/>
-      <c r="D135" s="22"/>
-      <c r="E135" s="22"/>
-      <c r="F135" s="22"/>
-      <c r="G135" s="22"/>
-      <c r="H135" s="22"/>
-    </row>
-    <row r="136" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B136" s="23" t="s">
-        <v>219</v>
-      </c>
-      <c r="C136" s="22"/>
-      <c r="D136" s="22"/>
-      <c r="E136" s="22"/>
-      <c r="F136" s="22"/>
-      <c r="G136" s="22"/>
-      <c r="H136" s="22"/>
-    </row>
-    <row r="137" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B137" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="C137" s="22"/>
-      <c r="D137" s="22"/>
-      <c r="E137" s="22"/>
-      <c r="F137" s="22"/>
-      <c r="G137" s="22"/>
-      <c r="H137" s="22"/>
-    </row>
-    <row r="138" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B138" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="C138" s="22"/>
-      <c r="D138" s="22"/>
-      <c r="E138" s="22"/>
-      <c r="F138" s="22"/>
-      <c r="G138" s="22"/>
-      <c r="H138" s="22"/>
-    </row>
-    <row r="141" ht="15">
-      <c r="B141" s="22" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="156" ht="15">
-      <c r="B156" s="22" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="157" ht="15">
-      <c r="B157" s="22" t="s">
-        <v>224</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B138:H138"/>
-    <mergeCell ref="B133:H133"/>
-    <mergeCell ref="B134:H134"/>
-    <mergeCell ref="B135:H135"/>
-    <mergeCell ref="B136:H136"/>
-    <mergeCell ref="B137:H137"/>
+  <mergeCells count="8">
+    <mergeCell ref="B119:H119"/>
+    <mergeCell ref="B120:H120"/>
+    <mergeCell ref="B121:H121"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B128:I128"/>
-    <mergeCell ref="B132:I132"/>
+    <mergeCell ref="B117:I117"/>
+    <mergeCell ref="B118:H118"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
